--- a/CLASS WORK/HLOOKUP.xlsx
+++ b/CLASS WORK/HLOOKUP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CLASS WORK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jit\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70BC1EDC-5E6E-4E83-A044-3D682704F4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{475E2BE4-5E62-4B38-951F-438477ADBDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
   <si>
     <t>Jan</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Product F</t>
   </si>
   <si>
-    <t>Question</t>
-  </si>
-  <si>
     <t>1. Sales for Product A in March</t>
   </si>
   <si>
@@ -98,14 +95,35 @@
     <t>Product</t>
   </si>
   <si>
-    <t>Answers</t>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Maximum Sales</t>
+  </si>
+  <si>
+    <t>Minimum Sales</t>
+  </si>
+  <si>
+    <t>Average Sales</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,8 +139,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,13 +157,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.499984740745262"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -169,15 +201,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -482,218 +517,485 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" customWidth="1"/>
-    <col min="9" max="9" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="11.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="3" customWidth="1"/>
+    <col min="9" max="13" width="8.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>120</v>
+      </c>
+      <c r="C2" s="2">
+        <v>130</v>
+      </c>
+      <c r="D2" s="2">
+        <v>140</v>
+      </c>
+      <c r="E2" s="2">
+        <v>150</v>
+      </c>
+      <c r="F2" s="2">
+        <v>160</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>150</v>
+      </c>
+      <c r="C3" s="2">
+        <v>160</v>
+      </c>
+      <c r="D3" s="2">
+        <v>170</v>
+      </c>
+      <c r="E3" s="2">
+        <v>180</v>
+      </c>
+      <c r="F3" s="2">
+        <v>190</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2">
+        <f>HLOOKUP(I$2,$B$1:$F$7,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="J3" s="2">
+        <f>HLOOKUP(J$2,$B$1:$F$7,2,0)</f>
+        <v>130</v>
+      </c>
+      <c r="K3" s="2">
+        <f>HLOOKUP(K$2,$B$1:$F$7,2,0)</f>
+        <v>140</v>
+      </c>
+      <c r="L3" s="2">
+        <f>HLOOKUP(L$2,$B$1:$F$7,2,0)</f>
+        <v>150</v>
+      </c>
+      <c r="M3" s="2">
+        <f>HLOOKUP(M$2,$B$1:$F$7,2,0)</f>
+        <v>160</v>
+      </c>
+      <c r="N3" s="2">
+        <f>SUM(I3:M3)</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2">
+        <v>210</v>
+      </c>
+      <c r="D4" s="2">
+        <v>220</v>
+      </c>
+      <c r="E4" s="2">
+        <v>230</v>
+      </c>
+      <c r="F4" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>90</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2">
+        <v>120</v>
+      </c>
+      <c r="F5" s="2">
+        <v>130</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <v>220</v>
+      </c>
+      <c r="C6" s="2">
+        <v>230</v>
+      </c>
+      <c r="D6" s="2">
+        <v>240</v>
+      </c>
+      <c r="E6" s="2">
+        <v>250</v>
+      </c>
+      <c r="F6" s="2">
+        <v>260</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2">
+        <v>130</v>
+      </c>
+      <c r="C7" s="2">
+        <v>140</v>
+      </c>
+      <c r="D7" s="2">
+        <v>150</v>
+      </c>
+      <c r="E7" s="2">
+        <v>160</v>
+      </c>
+      <c r="F7" s="2">
+        <v>170</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="2">
+        <f>HLOOKUP(I$6,$B$1:$F$7,3,0)</f>
+        <v>150</v>
+      </c>
+      <c r="J7" s="2">
+        <f>HLOOKUP(J$6,$B$1:$F$7,3,0)</f>
+        <v>160</v>
+      </c>
+      <c r="K7" s="2">
+        <f>HLOOKUP(K$6,$B$1:$F$7,3,0)</f>
+        <v>170</v>
+      </c>
+      <c r="L7" s="2">
+        <f>HLOOKUP(L$6,$B$1:$F$7,3,0)</f>
+        <v>180</v>
+      </c>
+      <c r="M7" s="2">
+        <f>HLOOKUP(M$6,$B$1:$F$7,3,0)</f>
+        <v>190</v>
+      </c>
+      <c r="N7" s="2">
+        <f>MAX(I7:M7)</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="J10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="K10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="L10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="M10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="N10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
-        <v>120</v>
-      </c>
-      <c r="C2" s="1">
-        <v>130</v>
-      </c>
-      <c r="D2" s="1">
-        <v>140</v>
-      </c>
-      <c r="E2" s="1">
-        <v>150</v>
-      </c>
-      <c r="F2" s="1">
-        <v>160</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2">
         <f>HLOOKUP("Mar",$A$1:$F$7,2,0)</f>
         <v>140</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="H11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
+      <c r="I11" s="2">
+        <f>HLOOKUP(I$10,$B$1:$F$7,7,0)</f>
+        <v>130</v>
+      </c>
+      <c r="J11" s="2">
+        <f>HLOOKUP(J$10,$B$1:$F$7,7,0)</f>
+        <v>140</v>
+      </c>
+      <c r="K11" s="2">
+        <f>HLOOKUP(K$10,$B$1:$F$7,7,0)</f>
         <v>150</v>
       </c>
-      <c r="C3" s="1">
+      <c r="L11" s="2">
+        <f>HLOOKUP(L$10,$B$1:$F$7,7,0)</f>
         <v>160</v>
       </c>
-      <c r="D3" s="1">
+      <c r="M11" s="2">
+        <f>HLOOKUP(M$10,$B$1:$F$7,7,0)</f>
         <v>170</v>
       </c>
-      <c r="E3" s="1">
-        <v>180</v>
-      </c>
-      <c r="F3" s="1">
-        <v>190</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="N11" s="2">
+        <f>MIN(I11:M11)</f>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
         <f>HLOOKUP("May",$A$1:$F$7,5,0)</f>
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>200</v>
-      </c>
-      <c r="C4" s="1">
-        <v>210</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="H15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="2">
+        <f>HLOOKUP(I$14,$B$1:$F$7,6,0)</f>
         <v>220</v>
       </c>
-      <c r="E4" s="1">
+      <c r="J15" s="2">
+        <f>HLOOKUP(J$14,$B$1:$F$7,6,0)</f>
         <v>230</v>
       </c>
-      <c r="F4" s="1">
+      <c r="K15" s="2">
+        <f>HLOOKUP(K$14,$B$1:$F$7,6,0)</f>
         <v>240</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="L15" s="2">
+        <f>HLOOKUP(L$14,$B$1:$F$7,6,0)</f>
+        <v>250</v>
+      </c>
+      <c r="M15" s="2">
+        <f>HLOOKUP(M$14,$B$1:$F$7,6,0)</f>
+        <v>260</v>
+      </c>
+      <c r="N15" s="2">
+        <f>AVERAGE(I15:M15)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2">
         <f>HLOOKUP("Feb",$A$1:$F$7,4,0)</f>
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>90</v>
-      </c>
-      <c r="C5" s="1">
-        <v>100</v>
-      </c>
-      <c r="D5" s="1">
-        <v>110</v>
-      </c>
-      <c r="E5" s="1">
-        <v>120</v>
-      </c>
-      <c r="F5" s="1">
-        <v>130</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="1">
-        <f>SUM(HLOOKUP("Jan",A1:F7,2,0),HLOOKUP("Feb",A1:F7,2,0),HLOOKUP("Mar",A1:F7,2,0),HLOOKUP("Apr",A1:F7,2,0),HLOOKUP("May",A1:F7,2,0))</f>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1">
-        <v>220</v>
-      </c>
-      <c r="C6" s="1">
-        <v>230</v>
-      </c>
-      <c r="D6" s="1">
-        <v>240</v>
-      </c>
-      <c r="E6" s="1">
-        <v>250</v>
-      </c>
-      <c r="F6" s="1">
-        <v>260</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1">
-        <f>MAX(HLOOKUP("Jan",A1:F7,3,0),HLOOKUP("Feb",A1:F7,3,0),HLOOKUP("Mar",A1:F7,3,0),HLOOKUP("Apr",A1:F7,3,0),HLOOKUP("May",A1:F7,3,0))</f>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1">
-        <v>130</v>
-      </c>
-      <c r="C7" s="1">
-        <v>140</v>
-      </c>
-      <c r="D7" s="1">
-        <v>150</v>
-      </c>
-      <c r="E7" s="1">
-        <v>160</v>
-      </c>
-      <c r="F7" s="1">
-        <v>170</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="1">
-        <f>MIN(HLOOKUP("Jan",A1:F7,7,0),HLOOKUP("Feb",A1:F7,7,0),HLOOKUP("Mar",A1:F7,7,0),HLOOKUP("Apr",A1:F7,7,0),HLOOKUP("May",A1:F7,7,0))</f>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="1">
-        <f>AVERAGE(HLOOKUP("Jan",A1:F7,6,0),HLOOKUP("Feb",A1:F7,6,0),HLOOKUP("Mar",A1:F7,6,0),HLOOKUP("Apr",A1:F7,6,0),HLOOKUP("May",A1:F7,6,0))</f>
-        <v>240</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H1:N1"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H9:N9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>